--- a/excel/專案管理總表SDC.xlsx
+++ b/excel/專案管理總表SDC.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="WBS清單總表" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="下拉選單" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr/>
+  <calcPr fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>開始日期</t>
   </si>
@@ -52,13 +52,52 @@
     <t>進行中</t>
   </si>
   <si>
-    <t>團險專案</t>
-  </si>
-  <si>
-    <t>交付UAT</t>
+    <t>WBS_PROJECT1</t>
+  </si>
+  <si>
+    <t>團險系統專案</t>
+  </si>
+  <si>
+    <t>完成UAT</t>
   </si>
   <si>
     <t>Leo</t>
+  </si>
+  <si>
+    <t>WBS_PROJECT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">保戶 App 改版</t>
+  </si>
+  <si>
+    <t>App上架</t>
+  </si>
+  <si>
+    <t>Vincent</t>
+  </si>
+  <si>
+    <t>WBS_PROJECT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">核保 AI 升級</t>
+  </si>
+  <si>
+    <t>正式上線</t>
+  </si>
+  <si>
+    <t>Diana</t>
+  </si>
+  <si>
+    <t>WBS_PROJECT4</t>
+  </si>
+  <si>
+    <t>理賠數位化</t>
+  </si>
+  <si>
+    <t>Nelson</t>
+  </si>
+  <si>
+    <t>WBS_PROJECT5</t>
   </si>
   <si>
     <t>完成</t>
@@ -74,8 +113,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -102,8 +142,7 @@
     </font>
     <font>
       <u/>
-      <sz val="11.000000"/>
-      <color theme="10"/>
+      <color rgb="FF0563C1"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -112,7 +151,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -123,12 +162,6 @@
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor theme="5" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
@@ -144,34 +177,39 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="12">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="1" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -183,9 +221,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -671,7 +706,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" style="1" width="23.421875"/>
     <col customWidth="1" min="2" max="2" style="1" width="20.7109375"/>
@@ -680,43 +719,43 @@
     <col customWidth="1" min="5" max="5" style="1" width="14.7109375"/>
     <col customWidth="1" min="6" max="6" style="1" width="12.8515625"/>
     <col customWidth="1" min="7" max="7" style="1" width="24.421875"/>
-    <col customWidth="1" min="8" max="8" style="1" width="15.421875"/>
-    <col customWidth="1" min="9" max="10" style="1" width="14.7109375"/>
-    <col customWidth="1" min="11" max="11" style="1" width="15.00390625"/>
+    <col customWidth="1" min="8" max="8" style="2" width="15.421875"/>
+    <col customWidth="1" min="9" max="10" style="2" width="14.7109375"/>
+    <col customWidth="1" min="11" max="11" style="2" width="15.00390625"/>
     <col customWidth="1" min="12" max="12" width="17.00390625"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" ht="14.25">
-      <c r="A2" s="5">
+      <c r="H1" s="2"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+    </row>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="6">
         <v>46052</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -728,70 +767,136 @@
       <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="6">
         <v>46325</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="7"/>
-    </row>
-    <row r="3" ht="14.25">
-      <c r="A3" s="5">
+      <c r="G2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="A3" s="6">
         <v>46144</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="5">
+        <v>14</v>
+      </c>
+      <c r="E3" s="6">
         <v>46295</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="7"/>
-    </row>
-    <row r="4" ht="14.25">
-      <c r="K4" s="7"/>
-    </row>
-    <row r="5" ht="14.25">
-      <c r="K5" s="7"/>
-    </row>
-    <row r="6" ht="14.25">
-      <c r="K6" s="7"/>
-    </row>
-    <row r="7" ht="14.25">
+      <c r="G3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="A4" s="8">
+        <v>46054</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="8">
+        <v>46234</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="A5" s="8">
+        <v>46082</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="8">
+        <v>46387</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="8">
+        <v>46037</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="8">
+        <v>46264</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" s="2"/>
+    </row>
+    <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="K7" s="1"/>
+      <c r="H7" s="2"/>
+      <c r="K7" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="2" disablePrompts="0">
     <dataValidation sqref="F2:F29" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-      <formula1>下拉選單!$D$2:$D$31</formula1>
+      <formula1>下拉選單!$F$2:$F$31</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D29" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
-      <formula1>下拉選單!$C$2:$C$31</formula1>
+      <formula1>下拉選單!$D$2:$D$31</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="G2" tooltip=""/>
-    <hyperlink r:id="rId2" ref="G3" tooltip=""/>
+    <hyperlink r:id="rId1" ref="G2"/>
+    <hyperlink r:id="rId2" ref="G3"/>
+    <hyperlink r:id="rId3" ref="G4"/>
+    <hyperlink r:id="rId4" ref="G5"/>
+    <hyperlink r:id="rId5" ref="G6"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -802,51 +907,71 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="1" width="14.140625"/>
-    <col customWidth="1" min="2" max="2" style="1" width="27.57421875"/>
-    <col customWidth="1" min="3" max="3" style="1" width="15.00390625"/>
-    <col customWidth="1" min="4" max="4" style="1" width="18.00390625"/>
-    <col min="5" max="7" style="1" width="9.140625"/>
+    <col customWidth="1" min="1" max="1" style="2" width="14.140625"/>
+    <col customWidth="1" min="2" max="2" style="2" width="15.00390625"/>
+    <col customWidth="1" min="3" max="3" style="2" width="11.140625"/>
+    <col customWidth="1" min="4" max="4" style="2" width="18.00390625"/>
+    <col customWidth="1" min="5" max="5" style="2" width="12.57421875"/>
+    <col customWidth="1" min="6" max="6" style="2" width="32.7109375"/>
+    <col customWidth="1" min="7" max="7" style="2" width="15.28125"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25">
-      <c r="A1" s="1"/>
-      <c r="C1" s="8" t="s">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" ht="15">
-      <c r="A2" s="1"/>
-      <c r="C2" s="1" t="s">
+      <c r="G1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="F2" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="15">
-      <c r="A3" s="1"/>
-      <c r="C3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="9" t="s">
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="2"/>
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" ht="15">
-      <c r="A4" s="1"/>
-      <c r="D4" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" ht="15">
-      <c r="D5" s="9" t="s">
-        <v>16</v>
+      <c r="F3" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="2"/>
+      <c r="F4" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="F5" s="11" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
